--- a/data/trans_orig/IP36A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>16699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51824</t>
+          <t>51530</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>37435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>46268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>81111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95686</t>
+          <t>95494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181596</t>
+          <t>181370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190958</t>
+          <t>190932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>205468</t>
+          <t>205077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>215848</t>
+          <t>215552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390864</t>
+          <t>390880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404377</t>
+          <t>404364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40677</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46377</t>
+          <t>46480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35807</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79335</t>
+          <t>79724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86442</t>
+          <t>86403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271085</t>
+          <t>270916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>285947</t>
+          <t>285661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>284805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299997</t>
+          <t>299769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>561505</t>
+          <t>561257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>582048</t>
+          <t>581438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>27583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>48312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58109</t>
+          <t>58070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>47193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57111</t>
+          <t>56750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>99912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112307</t>
+          <t>112704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33277</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39993</t>
+          <t>40550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>62506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224962</t>
+          <t>225251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241486</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251966</t>
+          <t>251915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>267549</t>
+          <t>267627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>481310</t>
+          <t>481863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>504376</t>
+          <t>503819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54491</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60816</t>
+          <t>60787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53122</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60938</t>
+          <t>61112</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110856</t>
+          <t>110620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120411</t>
+          <t>120550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31567</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51590</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65970</t>
+          <t>66666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93981</t>
+          <t>94083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335276</t>
+          <t>335880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354515</t>
+          <t>354238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360852</t>
+          <t>360053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>379600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702663</t>
+          <t>702561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>730674</t>
+          <t>729978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>35177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42620</t>
+          <t>42830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41919</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82356</t>
+          <t>82914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>27554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59770</t>
+          <t>60360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>226074</t>
+          <t>226444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>239842</t>
+          <t>239366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221687</t>
+          <t>221289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238205</t>
+          <t>237452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452595</t>
+          <t>452005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>473938</t>
+          <t>473895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>55989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46379</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54433</t>
+          <t>54520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99679</t>
+          <t>99807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109506</t>
+          <t>109286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62753</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>89457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318887</t>
+          <t>318533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335070</t>
+          <t>334672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>308348</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329795</t>
+          <t>329003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>631980</t>
+          <t>631673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>658377</t>
+          <t>659597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29561</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57170</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40633</t>
+          <t>40264</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44315</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>74597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>163421</t>
+          <t>163161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185244</t>
+          <t>185179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154425</t>
+          <t>154794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173440</t>
+          <t>174104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>324584</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353651</t>
+          <t>353421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>43874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>55108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61063</t>
+          <t>60364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70319</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109177</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>205170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233550</t>
+          <t>232192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196825</t>
+          <t>197524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219708</t>
+          <t>220050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408990</t>
+          <t>410686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>447848</t>
+          <t>447906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP36A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>10370</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6199</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16035</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>11378</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7196</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16699</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6818</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16880</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10370</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6403</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15236</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42301</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>46472</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47348</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42027</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51530</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41846</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51908</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42301</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37435</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46268</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81111</t>
+          <t>83164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95494</t>
+          <t>96184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>52671</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>52671</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>52671</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>52671</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>52671</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>52671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10354</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5980</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16200</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8538</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4764</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14326</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4539</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13609</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10354</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16906</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211629</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205783</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>216003</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>187158</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>181370</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>190932</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>182087</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191157</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211629</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>205077</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>215552</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390880</t>
+          <t>390258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404364</t>
+          <t>404868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221983</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221983</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221983</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195696</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195696</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195696</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221983</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221983</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221983</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5094</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2583</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6318</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5806</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4682</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39576</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35882</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40976</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>44483</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40748</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>46480</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>41260</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>46381</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>39576</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>36294</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>40976</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79724</t>
+          <t>79412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86403</t>
+          <t>86568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40976</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40976</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40976</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>47066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>47066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>47066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40976</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>40976</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>40976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16332</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30481</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22499</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15827</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30572</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15685</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30786</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15861</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30825</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35680</t>
+          <t>35697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>293505</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>285149</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>299298</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>418</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>278989</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>270916</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>285661</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>270702</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>285803</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>293505</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>284805</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>299769</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>561257</t>
+          <t>561461</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>581438</t>
+          <t>581421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>301488</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6240</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15432</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10638</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16057</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16086</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10202</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6376</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15933</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52924</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47694</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56886</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53731</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48312</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>58070</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48283</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57762</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52924</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47193</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>56750</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99912</t>
+          <t>99368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112704</t>
+          <t>112352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>63126</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>63126</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63126</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>64369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>64369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>64369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>63126</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>63126</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>63126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25814</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18284</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35149</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24758</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17133</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32988</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17819</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33102</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>25814</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18502</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34214</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40550</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62506</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>260315</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>250980</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267845</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>233481</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>225251</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>241106</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>225137</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>240420</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>260315</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>251915</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267627</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>481863</t>
+          <t>480709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503819</t>
+          <t>503852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>286129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>286129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>286129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>372</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>258239</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>258239</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>258239</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>286129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>286129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>286129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9466</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7594</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7689</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5101</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9502</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58086</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53721</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61063</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>58493</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53999</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60787</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53904</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>60794</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,97%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58086</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53685</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>61112</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110620</t>
+          <t>110314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120550</t>
+          <t>120458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61593</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61593</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61593</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41117</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31626</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>51651</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>38497</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29964</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48322</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30332</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48868</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>41117</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32842</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52389</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66666</t>
+          <t>66123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94083</t>
+          <t>94443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>371325</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>360791</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>380816</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>345705</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>335880</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>354238</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>335334</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>353870</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>371325</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>360053</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>379600</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,03%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702561</t>
+          <t>702201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>729978</t>
+          <t>730521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>412442</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>412442</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>412442</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>553</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>384202</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>384202</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>384202</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>412442</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>412442</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>412442</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11014</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16312</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>33,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6490</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3147</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10800</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10677</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11014</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17002</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37460</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32162</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41808</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>39487</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35177</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42830</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>35300</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>85,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37460</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>31472</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>41669</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70153</t>
+          <t>70789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48474</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48474</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48474</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>45977</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>45977</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>45977</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>48474</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>48474</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>48474</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19853</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36549</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>20416</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14632</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27554</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14169</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27473</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>27842</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>20915</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>37078</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60360</t>
+          <t>60231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>230525</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>221818</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>238514</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>352</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>233582</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>226444</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>239366</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>226525</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>239829</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>230525</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>221289</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>237452</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,22%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452005</t>
+          <t>452134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>473895</t>
+          <t>473738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258367</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258367</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258367</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>385</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253998</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253998</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253998</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258367</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258367</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10648</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2978</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6930</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5821</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2647</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10907</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51346</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46519</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54549</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>54169</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50217</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55989</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>50652</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56042</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51346</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>46260</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>54520</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99807</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109286</t>
+          <t>109530</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57167</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57167</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57167</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>57147</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>57147</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>57147</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>57167</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>57167</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>57167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34909</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56409</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>29884</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22450</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38589</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22178</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39283</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>44676</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>35004</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>55841</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>63317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89457</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>319331</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>307598</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>329098</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>489</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>327238</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>318533</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>334672</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>317839</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>334944</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>319331</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>308166</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>329003</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>631673</t>
+          <t>630013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>659597</t>
+          <t>657813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>357122</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>357122</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>357122</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11983</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7381</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17296</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,79%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11316</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5293</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18709</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,09%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23484</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18171</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28086</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,21%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>51,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23924</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16531</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>67,89%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,91%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>19760</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48813</t>
+          <t>43243</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39278</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56446</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35467</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35467</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35467</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>35240</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>35240</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35240</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>73155</t>
+          <t>64285</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73155</t>
+          <t>64285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73155</t>
+          <t>64285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28455</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20579</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38878</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28805</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17729</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39747</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40264</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58632</t>
+          <t>57947</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44545</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74597</t>
+          <t>72042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>149393</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>138970</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>157269</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>174103</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>163161</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>185179</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>165231</t>
+          <t>145415</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154794</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174104</t>
+          <t>153167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>339334</t>
+          <t>294808</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323369</t>
+          <t>280713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353421</t>
+          <t>305885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>177848</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177848</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177848</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>202908</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>202908</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>202908</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195058</t>
+          <t>174906</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>195058</t>
+          <t>174906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>195058</t>
+          <t>174906</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>397966</t>
+          <t>352755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>397966</t>
+          <t>352755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>397966</t>
+          <t>352755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2159</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9514</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4972</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4396</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5198</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2256</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9374</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17959</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13438</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20793</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20854</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>17158</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20745</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>17736</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22132</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>80,14%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19718</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15542</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,14%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>62,38%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>56</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>40572</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43874</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45084</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45084</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45431</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35136</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56314</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28086</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55108</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>85368</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70261</t>
+          <t>71378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107481</t>
+          <t>101591</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>190836</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>179953</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201131</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>218881</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>205170</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>232192</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>209837</t>
+          <t>185920</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197524</t>
+          <t>174381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220050</t>
+          <t>195630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>428719</t>
+          <t>376756</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>410686</t>
+          <t>360533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>447906</t>
+          <t>390746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
